--- a/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/IOT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="92">
   <si>
     <t>IOT</t>
   </si>
@@ -656,362 +656,387 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45962</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45871</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45780</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45689</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45598</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45507</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45416</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45325</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44135</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>44044</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43953</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>508400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>478800</v>
+      </c>
+      <c r="F8" s="3">
         <v>444300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>416000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>391500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>366900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>346300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>322000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>300200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>280700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>276300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>237500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>219300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>204300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>186600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>169800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>153500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>142600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>125800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>113800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>101000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>87700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>75900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>66200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>56800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>51000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>115700</v>
+      </c>
+      <c r="E9" s="3">
+        <v>117400</v>
+      </c>
+      <c r="F9" s="3">
         <v>104900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>96800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>90200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>82800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>79300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>75700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>73200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>68200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>68200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>61400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>58600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>57600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>51500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>47300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>44300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>39600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>38700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>31800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>28400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>25600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>21200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>18700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>18900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>16600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>16100</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>392800</v>
+      </c>
+      <c r="E10" s="3">
+        <v>361400</v>
+      </c>
+      <c r="F10" s="3">
         <v>339400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>319200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>301300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>284100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>267000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>246300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>227000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>212500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>208100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>176100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>160600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>146800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>135100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>122500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>109200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>103000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>87100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>82000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>72600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>62100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>54700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>47500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>37900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>34400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1040,88 +1065,96 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>102600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>97600</v>
+      </c>
+      <c r="F12" s="3">
         <v>89500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>86200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>85600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>83200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>73300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>77000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>76500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>73000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>73400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>60800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>64000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>60400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>54600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>50000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>41800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>41000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>126500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>29700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>25500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>23500</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>20200</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>33500</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>21900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>24200</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>24000</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1200,8 +1233,14 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1217,54 +1256,54 @@
       <c r="G14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>3600</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>68700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>4800</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
@@ -1272,16 +1311,22 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>6800</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1289,44 +1334,44 @@
         <v>3300</v>
       </c>
       <c r="E15" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G15" s="3">
         <v>2400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>2100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>2500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>2600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>3300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>3600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>3700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1360,8 +1405,14 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,168 +1438,182 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>503600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>471600</v>
+      </c>
+      <c r="F17" s="3">
         <v>435300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>417700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>418100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>400100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>363400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>365700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>358400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>346700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>330600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>287500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>289000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>280100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>246600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>233300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>219300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>212900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>377500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>146100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>132300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>126300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>111200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>120500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>112900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>114700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>109900</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>7200</v>
+      </c>
+      <c r="F18" s="3">
         <v>9000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-26600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-33300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-17100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-43800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-58200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-66000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-54300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-50000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-69800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-75800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-60000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-63500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-65800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-70300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-251700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-32300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-31300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-38600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-35300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-56100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-68300</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1577,168 +1642,182 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-29800</v>
+      </c>
+      <c r="F20" s="3">
         <v>-7100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>100</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R20" s="3">
         <v>8500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-800</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>40100</v>
+      </c>
+      <c r="F21" s="3">
         <v>19500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="F21" s="3">
-        <v>-24500</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>-24600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-29600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-15700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-40000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-55700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-63800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-51200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-46400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-66000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-72300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-48000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-54500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-61600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-67900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-249800</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-25400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-46000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1778,11 +1857,11 @@
       <c r="O22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1817,154 +1896,166 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>48900</v>
+      </c>
+      <c r="F23" s="3">
         <v>27500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>9100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-15200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-20500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-37300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-48600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-55900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-111500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-45400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-59500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-66900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-51500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-57900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-64200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-70300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-252000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-32400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-31000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-38400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-63600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>2600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>700</v>
-      </c>
-      <c r="R24" s="3">
-        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>700</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>700</v>
+      </c>
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
@@ -1975,10 +2066,16 @@
         <v>0</v>
       </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,168 +2154,186 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F26" s="3">
         <v>22000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>7800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-16800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-22100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-11200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-37800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-49600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-56300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-113400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-45500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-60000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-67900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-58600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-64300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-71000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-252800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-32400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-31400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-38400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F27" s="3">
         <v>22000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>7800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-16800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-22100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-37800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-49600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-56300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-113400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-45500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-60000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-67900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-58600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-64300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-71000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-252800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-32400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-31400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-38400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2412,14 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2377,8 +2498,14 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2584,14 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,168 +2670,186 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>29800</v>
+      </c>
+      <c r="F32" s="3">
         <v>7100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R32" s="3">
         <v>-8500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-5600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>800</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F33" s="3">
         <v>22000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>7800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-16800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-22100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-11200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-37800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-49600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-56300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-113400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-45500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-60000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-67900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-58600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-64300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-71000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-252800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-32400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-31400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-38400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,173 +2928,191 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F35" s="3">
         <v>22000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>7800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-16800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-22100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-11200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-37800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-49600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-56300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-113400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-45500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-60000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-67900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-58600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-64300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-71000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-252800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-32400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-31400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-38400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45962</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45871</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45780</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45689</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45598</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45507</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45416</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45325</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44135</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>44044</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43953</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3141,10 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,71 +3173,73 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>291400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>219000</v>
+      </c>
+      <c r="F41" s="3">
         <v>318800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>275100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>258500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>259000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>227600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>160300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>159300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>162500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>135500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>208100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>196000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>192100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>200700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>447000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>826100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>859800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>921200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>267500</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3082,59 +3255,65 @@
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>537500</v>
+      </c>
+      <c r="E42" s="3">
+        <v>585300</v>
+      </c>
+      <c r="F42" s="3">
         <v>515000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>486700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>443300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>439100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>467200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>511600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>513400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>431900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>412100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>451700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>528800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>533900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>489200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>291800</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3147,11 +3326,11 @@
       <c r="W42" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3162,71 +3341,77 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>345900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>291900</v>
+      </c>
+      <c r="F43" s="3">
         <v>327900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>262900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>253000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>222900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>240200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>184300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>183600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>148800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>166700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>119500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>118600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>105200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>122900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>90800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>77400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>84900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>82000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>59400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3242,71 +3427,77 @@
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>52200</v>
+      </c>
+      <c r="F44" s="3">
         <v>48200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>55000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>47600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>37900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>38900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>39400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>38600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>30500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>22200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>27100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>21800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>32400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>40600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>44500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>39100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>42000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>33100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>22300</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3322,71 +3513,77 @@
       <c r="AB44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>250700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>236700</v>
+      </c>
+      <c r="F45" s="3">
         <v>228400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>132000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>126700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>123300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>186400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>115100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>111300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>107800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>104000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>99200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>94100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>86300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>104200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>88900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>93400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>81900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>63900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>56800</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3402,71 +3599,77 @@
       <c r="AB45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1572800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1478300</v>
+      </c>
+      <c r="F46" s="3">
         <v>1507100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1258000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1186000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1132900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1212300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1039400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1039600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>923700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>887000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>940900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>978000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>970600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>957500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>963000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1036000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1068600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1100200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>406000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3482,59 +3685,65 @@
       <c r="AB46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>496800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>477100</v>
+      </c>
+      <c r="F47" s="3">
         <v>403100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>385300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>386300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>325100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>282700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>241100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>207700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>250600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>276200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>189400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>109700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>87800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>113100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>63700</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3547,11 +3756,11 @@
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3562,71 +3771,77 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>146300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>141700</v>
+      </c>
+      <c r="F48" s="3">
         <v>141900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>140700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>134400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>129900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>123000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>125600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>130200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>133300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>136900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>129100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>139900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>146500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>171900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>175900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>180100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>179200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>171200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>168800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3642,8 +3857,14 @@
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3675,20 +3896,20 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
         <v>13000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>11200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>9600</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -3722,8 +3943,14 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +4029,14 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,71 +4115,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>21800</v>
+      </c>
+      <c r="F52" s="3">
         <v>14900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>29100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>26400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>25100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>21200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>26900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>25800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>26100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>26400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>37800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>40100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>40100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>374500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>347400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>312900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>297100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>296600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>264700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3962,8 +4201,14 @@
       <c r="AB52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,71 +4287,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2769100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2614100</v>
+      </c>
+      <c r="F54" s="3">
         <v>2540700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2313700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2207100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2073600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2024300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1863900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1826100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1749400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1734800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1686400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1642600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1598500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1617000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1550000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1529000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1545000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1567900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>839500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4122,8 +4373,14 @@
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4409,10 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,71 +4441,73 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>41200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F57" s="3">
         <v>47700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>19800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>30100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>22300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>64000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>31500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>47300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>41200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>46300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>38300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>34700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>29200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>30100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>43400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>20400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>40800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>54700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>42300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4262,53 +4523,59 @@
       <c r="AB57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>12100</v>
+      </c>
+      <c r="F58" s="3">
         <v>12600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>12800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>12800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>14200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>15700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>18000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>19400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>20000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>20700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>20500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>16500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>10200</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4342,71 +4609,77 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>728900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>703900</v>
+      </c>
+      <c r="F59" s="3">
         <v>679300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>620900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>611300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>576500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>563300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>505600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>485900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>447000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>426400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>367400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>348800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>319100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>412000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>334500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>321400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>311500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>283600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>242100</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4422,71 +4695,77 @@
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>968100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>912100</v>
+      </c>
+      <c r="F60" s="3">
         <v>917000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>806400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>791600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>741200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>761300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>654100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>647200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>601300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>591800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>506500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>479300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>440900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>442200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>377800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>341800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>352300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>338300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>284400</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4502,53 +4781,59 @@
       <c r="AB60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>57000</v>
+      </c>
+      <c r="F61" s="3">
         <v>60200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>62800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>64400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>67900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>64600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>68000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>68300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>73600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>78800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>83300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>89400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>95200</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -4582,71 +4867,77 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F62" s="3">
         <v>13300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>7200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>7400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>9200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>9600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>9900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>9300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>9300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>9100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>236800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>232400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>234100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>230300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>240700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>235300</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4662,8 +4953,14 @@
       <c r="AB62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +5039,14 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +5125,14 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,71 +5211,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1167200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1106500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1120200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1010300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>992300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>946000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>955100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>864700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>861500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>825500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>819700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>735400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>706300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>676000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>679000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>610200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>575900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>582500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>579000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>519700</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4982,8 +5297,14 @@
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5333,10 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5415,14 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,8 +5501,14 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5229,14 +5564,14 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>949100</v>
       </c>
-      <c r="V70" s="3">
-        <v>0</v>
-      </c>
-      <c r="W70" s="3">
-        <v>0</v>
-      </c>
       <c r="X70" s="3">
         <v>0</v>
       </c>
@@ -5252,8 +5587,14 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,71 +5673,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1558400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-1574600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-1619100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-1641200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-1648900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-1632100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-1610000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-1598800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-1561000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-1511400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-1341700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-1296200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-1236200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-1168400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-1114800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-1056200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-991900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-921000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-668200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5412,8 +5759,14 @@
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5845,14 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5931,14 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,71 +6017,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1602000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1507600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1420400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1303400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1214800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1127600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1069200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>999100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>964700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>923900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>915100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>950900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>936400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>922600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>938000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>939800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>953100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>962400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>988900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-629200</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5732,8 +6103,14 @@
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,173 +6189,191 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46144</v>
+      </c>
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45962</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45871</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45780</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45689</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45598</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45507</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45416</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45325</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44135</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>44044</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43953</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43862</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F81" s="3">
         <v>22000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>7800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-16800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-22100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-11200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-37800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-49600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-56300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-113400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-45500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-60000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-67900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-58600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-64300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-71000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-252800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-32400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-31400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-38400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-36200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-54300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-56000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-63700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-67200</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,68 +6402,70 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>2600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>-100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>3600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>3700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>2400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>1400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>3400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>3300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>2600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>2400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>2200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>16</v>
       </c>
@@ -6081,14 +6478,20 @@
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6570,14 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6656,14 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6742,14 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6828,14 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,68 +6914,74 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>81400</v>
+      </c>
+      <c r="F89" s="3">
         <v>69700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>63700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>50200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>52600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>53900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>36000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>18100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>23700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-41900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>11900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>7700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>10500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-12900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-37000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-48800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-48300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6561,14 +6994,20 @@
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,73 +7036,75 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-8000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-6000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-6900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-5300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-4800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-3000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-10300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-6300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-10700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-9400</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>16</v>
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>16</v>
@@ -6671,14 +7112,20 @@
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +7204,14 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,68 +7290,74 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-149200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-54800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-48300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-68200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-18300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-33900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-36300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>3100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-42600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-16900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-17700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-249300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-365600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-6300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-10700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-9500</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6911,14 +7370,20 @@
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,8 +7412,10 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6988,11 +7455,11 @@
       <c r="O96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -7027,8 +7494,14 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7580,14 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7666,14 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,68 +7752,74 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-34400</v>
+      </c>
+      <c r="F100" s="3">
         <v>12000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>18400</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H100" s="3">
-        <v>11500</v>
       </c>
       <c r="I100" s="3">
         <v>-400</v>
       </c>
       <c r="J100" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K100" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L100" s="3">
         <v>15700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>9000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>12500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>6700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>9700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-1700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>703000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7341,73 +7832,79 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-200</v>
       </c>
       <c r="T101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>16</v>
+      <c r="U101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-200</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>16</v>
@@ -7421,74 +7918,80 @@
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-102600</v>
+      </c>
+      <c r="F102" s="3">
         <v>28500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>14900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>35100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>65200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-3000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>26900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-75000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>9700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>3800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-7400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-246400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-379100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-33700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-61400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>645100</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7501,10 +8004,16 @@
       <c r="Z102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>
